--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125107667</v>
+        <v>125106764</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489694</v>
+        <v>490063</v>
       </c>
       <c r="R2" t="n">
-        <v>6834844</v>
+        <v>6834930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125107049</v>
+        <v>125107287</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490157</v>
+        <v>490018</v>
       </c>
       <c r="R3" t="n">
-        <v>6834797</v>
+        <v>6834657</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106647</v>
+        <v>125107667</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -915,17 +930,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489944</v>
+        <v>489694</v>
       </c>
       <c r="R4" t="n">
-        <v>6834910</v>
+        <v>6834844</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125107287</v>
+        <v>125107049</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,53 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490018</v>
+        <v>490157</v>
       </c>
       <c r="R5" t="n">
-        <v>6834657</v>
+        <v>6834797</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106764</v>
+        <v>125106647</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490063</v>
+        <v>489944</v>
       </c>
       <c r="R7" t="n">
-        <v>6834930</v>
+        <v>6834910</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106764</v>
+        <v>125106146</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490063</v>
+        <v>489891</v>
       </c>
       <c r="R2" t="n">
-        <v>6834930</v>
+        <v>6835139</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125107287</v>
+        <v>125107049</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,53 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490018</v>
+        <v>490157</v>
       </c>
       <c r="R3" t="n">
-        <v>6834657</v>
+        <v>6834797</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -894,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125107667</v>
+        <v>125106647</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489694</v>
+        <v>489944</v>
       </c>
       <c r="R4" t="n">
-        <v>6834844</v>
+        <v>6834910</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125107049</v>
+        <v>125107287</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,38 +993,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490157</v>
+        <v>490018</v>
       </c>
       <c r="R5" t="n">
-        <v>6834797</v>
+        <v>6834657</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125106146</v>
+        <v>125107667</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489891</v>
+        <v>489694</v>
       </c>
       <c r="R6" t="n">
-        <v>6835139</v>
+        <v>6834844</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106647</v>
+        <v>125106764</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489944</v>
+        <v>490063</v>
       </c>
       <c r="R7" t="n">
-        <v>6834910</v>
+        <v>6834930</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106146</v>
+        <v>125107667</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489891</v>
+        <v>489694</v>
       </c>
       <c r="R2" t="n">
-        <v>6835139</v>
+        <v>6834844</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125107667</v>
+        <v>125106764</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1134,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489694</v>
+        <v>490063</v>
       </c>
       <c r="R6" t="n">
-        <v>6834844</v>
+        <v>6834930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106764</v>
+        <v>125106146</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490063</v>
+        <v>489891</v>
       </c>
       <c r="R7" t="n">
-        <v>6834930</v>
+        <v>6835139</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125107667</v>
+        <v>125106764</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489694</v>
+        <v>490063</v>
       </c>
       <c r="R2" t="n">
-        <v>6834844</v>
+        <v>6834930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125107049</v>
+        <v>125107667</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490157</v>
+        <v>489694</v>
       </c>
       <c r="R3" t="n">
-        <v>6834797</v>
+        <v>6834844</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106647</v>
+        <v>125106146</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489944</v>
+        <v>489891</v>
       </c>
       <c r="R4" t="n">
-        <v>6834910</v>
+        <v>6835139</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125106764</v>
+        <v>125106647</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490063</v>
+        <v>489944</v>
       </c>
       <c r="R6" t="n">
-        <v>6834930</v>
+        <v>6834910</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106146</v>
+        <v>125107049</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489891</v>
+        <v>490157</v>
       </c>
       <c r="R7" t="n">
-        <v>6835139</v>
+        <v>6834797</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106764</v>
+        <v>125106146</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490063</v>
+        <v>489891</v>
       </c>
       <c r="R2" t="n">
-        <v>6834930</v>
+        <v>6835139</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106146</v>
+        <v>125107287</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489891</v>
+        <v>490018</v>
       </c>
       <c r="R4" t="n">
-        <v>6835139</v>
+        <v>6834657</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125107287</v>
+        <v>125106647</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,53 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490018</v>
+        <v>489944</v>
       </c>
       <c r="R5" t="n">
-        <v>6834657</v>
+        <v>6834910</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125106647</v>
+        <v>125107049</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489944</v>
+        <v>490157</v>
       </c>
       <c r="R6" t="n">
-        <v>6834910</v>
+        <v>6834797</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125107049</v>
+        <v>125106764</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490157</v>
+        <v>490063</v>
       </c>
       <c r="R7" t="n">
-        <v>6834797</v>
+        <v>6834930</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106146</v>
+        <v>125106764</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489891</v>
+        <v>490063</v>
       </c>
       <c r="R2" t="n">
-        <v>6835139</v>
+        <v>6834930</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125107667</v>
+        <v>125106146</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489694</v>
+        <v>489891</v>
       </c>
       <c r="R3" t="n">
-        <v>6834844</v>
+        <v>6835139</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125107287</v>
+        <v>125107667</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,56 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490018</v>
+        <v>489694</v>
       </c>
       <c r="R4" t="n">
-        <v>6834657</v>
+        <v>6834844</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1098,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125107049</v>
+        <v>125107287</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1095,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490157</v>
+        <v>490018</v>
       </c>
       <c r="R6" t="n">
-        <v>6834797</v>
+        <v>6834657</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106764</v>
+        <v>125107049</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490063</v>
+        <v>490157</v>
       </c>
       <c r="R7" t="n">
-        <v>6834930</v>
+        <v>6834797</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106764</v>
+        <v>125107667</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490063</v>
+        <v>489694</v>
       </c>
       <c r="R2" t="n">
-        <v>6834930</v>
+        <v>6834844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125106146</v>
+        <v>125106764</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489891</v>
+        <v>490063</v>
       </c>
       <c r="R3" t="n">
-        <v>6835139</v>
+        <v>6834930</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125107667</v>
+        <v>125106647</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489694</v>
+        <v>489944</v>
       </c>
       <c r="R4" t="n">
-        <v>6834844</v>
+        <v>6834910</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125106647</v>
+        <v>125107287</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489944</v>
+        <v>490018</v>
       </c>
       <c r="R5" t="n">
-        <v>6834910</v>
+        <v>6834657</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125107287</v>
+        <v>125106146</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,53 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490018</v>
+        <v>489891</v>
       </c>
       <c r="R6" t="n">
-        <v>6834657</v>
+        <v>6835139</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125107667</v>
+        <v>125106764</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489694</v>
+        <v>490063</v>
       </c>
       <c r="R2" t="n">
-        <v>6834844</v>
+        <v>6834930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125106764</v>
+        <v>125106146</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490063</v>
+        <v>489891</v>
       </c>
       <c r="R3" t="n">
-        <v>6834930</v>
+        <v>6835139</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106647</v>
+        <v>125107287</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489944</v>
+        <v>490018</v>
       </c>
       <c r="R4" t="n">
-        <v>6834910</v>
+        <v>6834657</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125107287</v>
+        <v>125107667</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,56 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490018</v>
+        <v>489694</v>
       </c>
       <c r="R5" t="n">
-        <v>6834657</v>
+        <v>6834844</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125106146</v>
+        <v>125107049</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78684</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489891</v>
+        <v>490157</v>
       </c>
       <c r="R6" t="n">
-        <v>6835139</v>
+        <v>6834797</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125107049</v>
+        <v>125106647</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490157</v>
+        <v>489944</v>
       </c>
       <c r="R7" t="n">
-        <v>6834797</v>
+        <v>6834910</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 22412-2025 artfynd.xlsx
+++ b/artfynd/A 22412-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106764</v>
+        <v>125107287</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490063</v>
+        <v>490018</v>
       </c>
       <c r="R2" t="n">
-        <v>6834930</v>
+        <v>6834657</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125106146</v>
+        <v>125106647</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489891</v>
+        <v>489944</v>
       </c>
       <c r="R3" t="n">
-        <v>6835139</v>
+        <v>6834910</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125107287</v>
+        <v>125106764</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,56 +906,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490018</v>
+        <v>490063</v>
       </c>
       <c r="R4" t="n">
-        <v>6834657</v>
+        <v>6834930</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125107667</v>
+        <v>125106146</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,37 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännäset, Brännäset, Dlr</t>
+          <t>Ridaso, Ridaso, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489694</v>
+        <v>489891</v>
       </c>
       <c r="R5" t="n">
-        <v>6834844</v>
+        <v>6835139</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125106647</v>
+        <v>125107667</v>
       </c>
       <c r="B7" t="n">
         <v>78947</v>
@@ -1236,17 +1236,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ridaso, Ridaso, Dlr</t>
+          <t>Brännäset, Brännäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489944</v>
+        <v>489694</v>
       </c>
       <c r="R7" t="n">
-        <v>6834910</v>
+        <v>6834844</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
